--- a/car position.xlsx
+++ b/car position.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boaze\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boaze\Ai-Projects\parking systems\rotem-shani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7D0BCC-E29B-423B-BD88-45C85BE724B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6459E8F3-DB5D-4ECF-B3D8-0FB7B047B6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D0CD031-A119-4625-9AF9-4C97AA6C48F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
   <si>
     <t>Parking Number</t>
   </si>
@@ -68,60 +68,15 @@
     <t>E4</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>EL</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Parralel 14</t>
-  </si>
-  <si>
-    <t>Parralel 20</t>
-  </si>
-  <si>
     <t>Elevator</t>
   </si>
   <si>
-    <t>Opposite parking 1</t>
-  </si>
-  <si>
     <t>Opposite elvator</t>
   </si>
   <si>
@@ -129,16 +84,100 @@
   </si>
   <si>
     <t>P24</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>p4</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>Parralel P14</t>
+  </si>
+  <si>
+    <t>Parralel P20</t>
+  </si>
+  <si>
+    <t>Opposite parking P1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -536,7 +575,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="5" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.85546875" customWidth="1"/>
@@ -545,12 +585,12 @@
     <col min="29" max="29" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>3</v>
@@ -565,63 +605,65 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="3">
-        <v>20</v>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="3">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G6" s="3">
-        <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
@@ -629,12 +671,12 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>7</v>
@@ -645,23 +687,23 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
@@ -669,17 +711,17 @@
       <c r="F10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G10" s="3">
-        <v>5</v>
+      <c r="G10" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D11" s="2">
-        <v>1</v>
+    <row r="11" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
@@ -689,379 +731,318 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D12" s="2">
-        <v>2</v>
+    <row r="12" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="3">
-        <v>6</v>
-      </c>
-      <c r="G12" s="3">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3">
-        <v>9</v>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D13" s="2">
-        <v>3</v>
+    <row r="13" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="3">
-        <v>2</v>
-      </c>
-      <c r="G13" s="3">
-        <v>4</v>
+      <c r="F13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D14" s="2">
-        <v>4</v>
+    <row r="14" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D14" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="3">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="2">
-        <v>5</v>
+      <c r="F14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="3">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4</v>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D16" s="2">
-        <v>6</v>
+    <row r="16" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="3">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3">
-        <v>7</v>
+      <c r="F16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="K16" t="str">
-        <f>"P"&amp;F16</f>
-        <v>P2</v>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17" s="2">
-        <v>7</v>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D17" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="3">
-        <v>6</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8</v>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="K17" t="str">
-        <f t="shared" ref="K17:K30" si="0">"P"&amp;F17</f>
-        <v>P6</v>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18" s="2">
-        <v>8</v>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D18" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="3">
-        <v>7</v>
-      </c>
-      <c r="G18" s="3">
-        <v>22</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4</v>
+      <c r="F18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="I18" s="3"/>
-      <c r="K18" t="str">
-        <f t="shared" si="0"/>
-        <v>P7</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19" s="2">
-        <v>9</v>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3">
-        <v>10</v>
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="K19" t="str">
-        <f t="shared" si="0"/>
-        <v>P2</v>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20" s="2">
-        <v>10</v>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D20" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="3">
-        <v>9</v>
-      </c>
-      <c r="G20" s="3">
-        <v>11</v>
+      <c r="F20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="K20" t="str">
-        <f t="shared" si="0"/>
-        <v>P9</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="3">
-        <v>10</v>
-      </c>
-      <c r="G21" s="3">
-        <v>4</v>
+      <c r="F21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="K21" t="str">
-        <f t="shared" si="0"/>
-        <v>P10</v>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="3">
-        <v>15</v>
-      </c>
-      <c r="G22" s="3">
-        <v>13</v>
-      </c>
-      <c r="H22" s="3">
-        <v>18</v>
+      <c r="F22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="I22" s="3"/>
-      <c r="K22" t="str">
-        <f t="shared" si="0"/>
-        <v>P15</v>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="3">
-        <v>14</v>
-      </c>
-      <c r="G23" s="3">
-        <v>12</v>
+      <c r="F23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="K23" t="str">
-        <f t="shared" si="0"/>
-        <v>P14</v>
-      </c>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="3">
-        <v>17</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="K24" t="str">
-        <f t="shared" si="0"/>
-        <v>P17</v>
-      </c>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="3">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3">
-        <v>16</v>
+      <c r="F25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="K25" t="str">
-        <f t="shared" si="0"/>
-        <v>P12</v>
-      </c>
-    </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="3">
-        <v>17</v>
-      </c>
-      <c r="G26" s="3">
-        <v>15</v>
+      <c r="F26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="K26" t="str">
-        <f t="shared" si="0"/>
-        <v>P17</v>
-      </c>
-    </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="3">
-        <v>16</v>
-      </c>
-      <c r="G27" s="3">
-        <v>14</v>
+      <c r="F27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="K27" t="str">
-        <f t="shared" si="0"/>
-        <v>P16</v>
-      </c>
-    </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="3">
-        <v>12</v>
-      </c>
-      <c r="G28" s="3">
-        <v>19</v>
+      <c r="F28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="K28" t="str">
-        <f t="shared" si="0"/>
-        <v>P12</v>
-      </c>
-    </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="3">
-        <v>18</v>
-      </c>
-      <c r="G29" s="3">
-        <v>20</v>
+      <c r="F29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="K29" t="str">
-        <f t="shared" si="0"/>
-        <v>P18</v>
-      </c>
-    </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="3">
-        <v>19</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="F30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="I30" s="3"/>
-      <c r="K30" t="str">
-        <f t="shared" si="0"/>
-        <v>P19</v>
-      </c>
-    </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D32" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="3">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
-        <v>8</v>
+      <c r="F32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="K32" t="str">
-        <f>"P"&amp;F32</f>
-        <v>P5</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/car position.xlsx
+++ b/car position.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boaze\Ai-Projects\parking systems\rotem-shani\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Aiprojects\parking systems\rotem shani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6459E8F3-DB5D-4ECF-B3D8-0FB7B047B6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052D8D9C-F966-4DDD-89D6-36BAFF454993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D0CD031-A119-4625-9AF9-4C97AA6C48F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4D0CD031-A119-4625-9AF9-4C97AA6C48F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="43">
   <si>
     <t>Parking Number</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>Opposite parking P1</t>
+  </si>
+  <si>
+    <t>limitation</t>
+  </si>
+  <si>
+    <t>cant happen</t>
   </si>
 </sst>
 </file>
@@ -571,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F29CA4C-52C3-4F9A-87A1-F53221D74662}">
-  <dimension ref="D3:AC32"/>
+  <dimension ref="D3:AC36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="13.28515625" customWidth="1"/>
@@ -1041,6 +1047,33 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
+    <row r="34" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D34" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/car position.xlsx
+++ b/car position.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Aiprojects\parking systems\rotem shani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052D8D9C-F966-4DDD-89D6-36BAFF454993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB362128-FC11-4441-82DF-5868A2217860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4D0CD031-A119-4625-9AF9-4C97AA6C48F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
   <si>
     <t>Parking Number</t>
   </si>
@@ -674,7 +674,9 @@
       <c r="G7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="4:9" x14ac:dyDescent="0.25">
@@ -731,7 +733,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>

--- a/car position.xlsx
+++ b/car position.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Aiprojects\parking systems\rotem shani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB362128-FC11-4441-82DF-5868A2217860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AEDA4F-855C-4B68-AC80-AF63906D9407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4D0CD031-A119-4625-9AF9-4C97AA6C48F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="43">
   <si>
     <t>Parking Number</t>
   </si>
@@ -702,9 +702,7 @@
       <c r="E9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
         <v>9</v>
       </c>
